--- a/artfynd/A 11794-2025 artfynd.xlsx
+++ b/artfynd/A 11794-2025 artfynd.xlsx
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115628649</v>
+        <v>115628528</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>319342</v>
+        <v>319263</v>
       </c>
       <c r="R2" t="n">
-        <v>6436615</v>
+        <v>6436614</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,12 +779,7 @@
         <v>115628403</v>
       </c>
       <c r="B3" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115628676</v>
+        <v>115628649</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,7 +912,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>319273</v>
+        <v>319342</v>
       </c>
       <c r="R4" t="n">
-        <v>6436670</v>
+        <v>6436615</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +981,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mathias Molau, Jeanette Karlsson, Tilda Lindkvist, Johanna Ek, Robert Petersen, Sandra Johansson</t>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1011,12 +991,7 @@
         <v>115628675</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,49 +1087,49 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mathias Molau, Jeanette Karlsson, Tilda Lindkvist, Johanna Ek, Robert Petersen, Sandra Johansson</t>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115628528</v>
+        <v>115628676</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>319263</v>
+        <v>319273</v>
       </c>
       <c r="R6" t="n">
-        <v>6436614</v>
+        <v>6436670</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1193,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mathias Molau, Jeanette Karlsson, Tilda Lindkvist, Johanna Ek, Robert Petersen, Sandra Johansson</t>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 11794-2025 artfynd.xlsx
+++ b/artfynd/A 11794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628528</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628675</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115628676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>